--- a/branches/fix/example-references/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/fix/example-references/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T19:30:57+00:00</t>
+    <t>2026-09-09T06:38:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/example-references/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
+++ b/branches/fix/example-references/CodeSystem-mii-cs-medikation-pzn-sales-status-code.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T06:38:41+00:00</t>
+    <t>2026-09-09T07:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
